--- a/ResourcesBD/distributorProfileBulkUpdate.xlsx
+++ b/ResourcesBD/distributorProfileBulkUpdate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JAR\ResourcesBD\"/>
     </mc:Choice>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>Distributor Code*</t>
   </si>
@@ -124,6 +124,36 @@
   </si>
   <si>
     <t>MON</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTIONCE23</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTION249D</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTION1F9E</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTIONADD8</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTION25BF</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTION4A4B</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTIONA3D3</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTION4139</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTIONC4F3</t>
+  </si>
+  <si>
+    <t>M/S. ATLANTIC DISTRIBUTIONB211</t>
   </si>
 </sst>
 </file>
@@ -450,29 +480,29 @@
   <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="1"/>
-    <col min="8" max="11" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8" style="1"/>
-    <col min="18" max="20" width="8" style="1"/>
-    <col min="24" max="24" width="26.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="27.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="32.81640625"/>
+    <col min="5" max="6" bestFit="true" customWidth="true" style="2" width="24.0"/>
+    <col min="7" max="7" style="1" width="8.0"/>
+    <col min="8" max="11" bestFit="true" customWidth="true" style="2" width="24.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="31.1796875"/>
+    <col min="15" max="15" style="1" width="8.0"/>
+    <col min="18" max="20" style="1" width="8.0"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="2" width="26.1796875"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="10.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -496,22 +526,22 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" t="s" s="0">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -523,13 +553,13 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" t="s" s="0">
         <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
@@ -540,16 +570,16 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>28</v>
       </c>
       <c r="E2" s="2">
@@ -558,8 +588,8 @@
       <c r="F2" s="2">
         <v>60.5351</v>
       </c>
-      <c r="G2" s="1">
-        <v>4</v>
+      <c r="G2" s="1" t="n">
+        <v>38.0</v>
       </c>
       <c r="H2" s="2">
         <v>60.5351</v>
@@ -573,10 +603,10 @@
       <c r="K2" s="2">
         <v>60.5351</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>29</v>
       </c>
       <c r="N2" s="3" t="s">
@@ -585,10 +615,10 @@
       <c r="O2" s="1">
         <v>1</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>29</v>
       </c>
       <c r="R2" s="1">
@@ -600,13 +630,13 @@
       <c r="T2" s="1">
         <v>5</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>29</v>
       </c>
       <c r="X2" s="2">

--- a/ResourcesBD/distributorProfileBulkUpdate.xlsx
+++ b/ResourcesBD/distributorProfileBulkUpdate.xlsx
@@ -589,7 +589,7 @@
         <v>60.5351</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>38.0</v>
+        <v>17.0</v>
       </c>
       <c r="H2" s="2">
         <v>60.5351</v>
